--- a/Design/Excel/ET/Datas/Game/Items.xlsx
+++ b/Design/Excel/ET/Datas/Game/Items.xlsx
@@ -8,19 +8,20 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\ugit\myGameDevelopmentKit\Design\Excel\ET\Datas\Game\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B2D2F1D-6B6E-4232-9B4D-AB2730195C5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACA39AAC-D8CD-4F8C-BF7A-8F06E82246F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6860" yWindow="730" windowWidth="19200" windowHeight="9970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2660" yWindow="2660" windowWidth="19200" windowHeight="9970" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Herb" sheetId="2" r:id="rId1"/>
+    <sheet name="Weapon" sheetId="3" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="99">
   <si>
     <t>##var</t>
   </si>
@@ -297,6 +298,49 @@
   <si>
     <t>AreaName</t>
     <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>玄铁飞剑</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>围绕在身边的飞剑</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>掉落</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>天剑宗</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>ItemType</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>类型</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Attr</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>属性</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>10061,10;10081,10</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>##type</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>map,int,long</t>
   </si>
 </sst>
 </file>
@@ -445,7 +489,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="差" xfId="3" builtinId="27"/>
@@ -753,18 +797,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:H23"/>
+  <dimension ref="A1:J23"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="6.26953125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.90625" customWidth="1"/>
-    <col min="4" max="4" width="7.81640625" customWidth="1"/>
-    <col min="5" max="5" width="11.08984375" customWidth="1"/>
-    <col min="7" max="7" width="9.90625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17.81640625" customWidth="1"/>
+    <col min="3" max="3" width="8.90625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.90625" customWidth="1"/>
+    <col min="5" max="5" width="7.81640625" customWidth="1"/>
+    <col min="6" max="6" width="11.08984375" customWidth="1"/>
+    <col min="8" max="8" width="9.90625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="15.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -772,23 +817,29 @@
         <v>7</v>
       </c>
       <c r="C1" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="E1" s="2"/>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="2"/>
+      <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="H1" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="I1" s="2" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" ht="15.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="J1" s="2" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="5" t="s">
         <v>1</v>
       </c>
@@ -799,501 +850,576 @@
         <v>2</v>
       </c>
       <c r="D2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="E2" s="2"/>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="2"/>
+      <c r="G2" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="H2" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="H2" s="7" t="s">
+      <c r="I2" s="2" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" ht="15.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="J2" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="3" t="s">
         <v>3</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>4</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>81</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="F3" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="G3" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="H3" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="H3" s="7" t="s">
+      <c r="I3" s="2" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="J3" s="2" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
       <c r="B4" s="6">
         <v>10001</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="6">
+        <v>1</v>
+      </c>
+      <c r="D4" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="6">
+      <c r="E4" s="6">
         <v>1001</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="F4" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="F4" s="6">
+      <c r="G4" s="6">
         <v>5</v>
       </c>
-      <c r="G4" s="6" t="s">
+      <c r="H4" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="H4" s="6" t="s">
+      <c r="I4" s="6" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="6">
         <v>10002</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="6">
+        <v>1</v>
+      </c>
+      <c r="D5" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="D5" s="6">
+      <c r="E5" s="6">
         <v>1001</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="F5" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="F5" s="6">
+      <c r="G5" s="6">
         <v>8</v>
       </c>
-      <c r="G5" s="6" t="s">
+      <c r="H5" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="H5" s="6" t="s">
+      <c r="I5" s="6" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B6" s="6">
         <v>10003</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="6">
+        <v>1</v>
+      </c>
+      <c r="D6" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="D6" s="6">
+      <c r="E6" s="6">
         <v>1002</v>
       </c>
-      <c r="E6" s="6" t="s">
+      <c r="F6" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="F6" s="6">
+      <c r="G6" s="6">
         <v>12</v>
       </c>
-      <c r="G6" s="6" t="s">
+      <c r="H6" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="H6" s="6" t="s">
+      <c r="I6" s="6" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B7" s="6">
         <v>10004</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="6">
+        <v>1</v>
+      </c>
+      <c r="D7" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="D7" s="6">
+      <c r="E7" s="6">
         <v>1002</v>
       </c>
-      <c r="E7" s="6" t="s">
+      <c r="F7" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="F7" s="6">
+      <c r="G7" s="6">
         <v>15</v>
       </c>
-      <c r="G7" s="6" t="s">
+      <c r="H7" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="H7" s="6" t="s">
+      <c r="I7" s="6" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B8" s="6">
         <v>10005</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="C8" s="6">
+        <v>1</v>
+      </c>
+      <c r="D8" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="D8" s="6">
+      <c r="E8" s="6">
         <v>1003</v>
       </c>
-      <c r="E8" s="6" t="s">
+      <c r="F8" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="F8" s="6">
+      <c r="G8" s="6">
         <v>25</v>
       </c>
-      <c r="G8" s="6" t="s">
+      <c r="H8" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="H8" s="6" t="s">
+      <c r="I8" s="6" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B9" s="6">
         <v>10006</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="C9" s="6">
+        <v>1</v>
+      </c>
+      <c r="D9" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="D9" s="6">
+      <c r="E9" s="6">
         <v>1003</v>
       </c>
-      <c r="E9" s="6" t="s">
+      <c r="F9" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="F9" s="6">
+      <c r="G9" s="6">
         <v>25</v>
       </c>
-      <c r="G9" s="6" t="s">
+      <c r="H9" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="H9" s="6" t="s">
+      <c r="I9" s="6" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B10" s="6">
         <v>10007</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="C10" s="6">
+        <v>1</v>
+      </c>
+      <c r="D10" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="D10" s="6">
+      <c r="E10" s="6">
         <v>1003</v>
       </c>
-      <c r="E10" s="6" t="s">
+      <c r="F10" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="F10" s="6">
+      <c r="G10" s="6">
         <v>30</v>
       </c>
-      <c r="G10" s="6" t="s">
+      <c r="H10" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="H10" s="6" t="s">
+      <c r="I10" s="6" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B11" s="6">
         <v>10008</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="C11" s="6">
+        <v>1</v>
+      </c>
+      <c r="D11" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="D11" s="6">
+      <c r="E11" s="6">
         <v>2001</v>
       </c>
-      <c r="E11" s="6" t="s">
+      <c r="F11" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="F11" s="6">
+      <c r="G11" s="6">
         <v>50</v>
       </c>
-      <c r="G11" s="6" t="s">
+      <c r="H11" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="H11" s="6" t="s">
+      <c r="I11" s="6" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B12" s="6">
         <v>10009</v>
       </c>
-      <c r="C12" s="6" t="s">
+      <c r="C12" s="6">
+        <v>1</v>
+      </c>
+      <c r="D12" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="D12" s="6">
+      <c r="E12" s="6">
         <v>2001</v>
       </c>
-      <c r="E12" s="6" t="s">
+      <c r="F12" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="F12" s="6">
+      <c r="G12" s="6">
         <v>60</v>
       </c>
-      <c r="G12" s="6" t="s">
+      <c r="H12" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="H12" s="6" t="s">
+      <c r="I12" s="6" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B13" s="6">
         <v>10010</v>
       </c>
-      <c r="C13" s="6" t="s">
+      <c r="C13" s="6">
+        <v>1</v>
+      </c>
+      <c r="D13" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="D13" s="6">
+      <c r="E13" s="6">
         <v>2002</v>
       </c>
-      <c r="E13" s="6" t="s">
+      <c r="F13" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="F13" s="6">
+      <c r="G13" s="6">
         <v>80</v>
       </c>
-      <c r="G13" s="6" t="s">
+      <c r="H13" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="H13" s="6" t="s">
+      <c r="I13" s="6" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B14" s="6">
         <v>10011</v>
       </c>
-      <c r="C14" s="6" t="s">
+      <c r="C14" s="6">
+        <v>1</v>
+      </c>
+      <c r="D14" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="D14" s="6">
+      <c r="E14" s="6">
         <v>2002</v>
       </c>
-      <c r="E14" s="6" t="s">
+      <c r="F14" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="F14" s="6">
+      <c r="G14" s="6">
         <v>100</v>
       </c>
-      <c r="G14" s="6" t="s">
+      <c r="H14" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="H14" s="6" t="s">
+      <c r="I14" s="6" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B15" s="6">
         <v>10012</v>
       </c>
-      <c r="C15" s="6" t="s">
+      <c r="C15" s="6">
+        <v>1</v>
+      </c>
+      <c r="D15" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="D15" s="6">
+      <c r="E15" s="6">
         <v>2002</v>
       </c>
-      <c r="E15" s="6" t="s">
+      <c r="F15" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="F15" s="6">
+      <c r="G15" s="6">
         <v>100</v>
       </c>
-      <c r="G15" s="6" t="s">
+      <c r="H15" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="H15" s="6" t="s">
+      <c r="I15" s="6" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="28" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B16" s="6">
         <v>10013</v>
       </c>
-      <c r="C16" s="6" t="s">
+      <c r="C16" s="6">
+        <v>1</v>
+      </c>
+      <c r="D16" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="D16" s="6">
+      <c r="E16" s="6">
         <v>2003</v>
       </c>
-      <c r="E16" s="6" t="s">
+      <c r="F16" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="F16" s="6">
+      <c r="G16" s="6">
         <v>150</v>
       </c>
-      <c r="G16" s="6" t="s">
+      <c r="H16" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="H16" s="6" t="s">
+      <c r="I16" s="6" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B17" s="6">
         <v>10014</v>
       </c>
-      <c r="C17" s="6" t="s">
+      <c r="C17" s="6">
+        <v>1</v>
+      </c>
+      <c r="D17" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="D17" s="6">
+      <c r="E17" s="6">
         <v>2003</v>
       </c>
-      <c r="E17" s="6" t="s">
+      <c r="F17" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="F17" s="6">
+      <c r="G17" s="6">
         <v>200</v>
       </c>
-      <c r="G17" s="6" t="s">
+      <c r="H17" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="H17" s="6" t="s">
+      <c r="I17" s="6" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B18" s="6">
         <v>10015</v>
       </c>
-      <c r="C18" s="6" t="s">
+      <c r="C18" s="6">
+        <v>1</v>
+      </c>
+      <c r="D18" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="D18" s="6">
+      <c r="E18" s="6">
         <v>3001</v>
       </c>
-      <c r="E18" s="6" t="s">
+      <c r="F18" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="F18" s="6">
+      <c r="G18" s="6">
         <v>500</v>
       </c>
-      <c r="G18" s="6" t="s">
+      <c r="H18" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="H18" s="6" t="s">
+      <c r="I18" s="6" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B19" s="6">
         <v>10016</v>
       </c>
-      <c r="C19" s="6" t="s">
+      <c r="C19" s="6">
+        <v>1</v>
+      </c>
+      <c r="D19" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="D19" s="6">
+      <c r="E19" s="6">
         <v>3002</v>
       </c>
-      <c r="E19" s="6" t="s">
+      <c r="F19" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="F19" s="6">
+      <c r="G19" s="6">
         <v>800</v>
       </c>
-      <c r="G19" s="6" t="s">
+      <c r="H19" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="H19" s="6" t="s">
+      <c r="I19" s="6" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="20" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B20" s="6">
         <v>10017</v>
       </c>
-      <c r="C20" s="6" t="s">
+      <c r="C20" s="6">
+        <v>1</v>
+      </c>
+      <c r="D20" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="D20" s="6">
+      <c r="E20" s="6">
         <v>3002</v>
       </c>
-      <c r="E20" s="6" t="s">
+      <c r="F20" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="F20" s="6">
+      <c r="G20" s="6">
         <v>900</v>
       </c>
-      <c r="G20" s="6" t="s">
+      <c r="H20" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="H20" s="6" t="s">
+      <c r="I20" s="6" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="21" spans="2:8" ht="28" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B21" s="6">
         <v>10018</v>
       </c>
-      <c r="C21" s="6" t="s">
+      <c r="C21" s="6">
+        <v>1</v>
+      </c>
+      <c r="D21" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="D21" s="6">
+      <c r="E21" s="6">
         <v>3003</v>
       </c>
-      <c r="E21" s="6" t="s">
+      <c r="F21" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="F21" s="6">
+      <c r="G21" s="6">
         <v>1500</v>
       </c>
-      <c r="G21" s="6" t="s">
+      <c r="H21" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="H21" s="6" t="s">
+      <c r="I21" s="6" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B22" s="6">
         <v>10019</v>
       </c>
-      <c r="C22" s="6" t="s">
+      <c r="C22" s="6">
+        <v>1</v>
+      </c>
+      <c r="D22" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="D22" s="6">
+      <c r="E22" s="6">
         <v>4001</v>
       </c>
-      <c r="E22" s="6" t="s">
+      <c r="F22" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="F22" s="6">
+      <c r="G22" s="6">
         <v>3000</v>
       </c>
-      <c r="G22" s="6" t="s">
+      <c r="H22" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="H22" s="6" t="s">
+      <c r="I22" s="6" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B23" s="6">
         <v>10020</v>
       </c>
-      <c r="C23" s="6" t="s">
+      <c r="C23" s="6">
+        <v>1</v>
+      </c>
+      <c r="D23" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="D23" s="6">
+      <c r="E23" s="6">
         <v>5001</v>
       </c>
-      <c r="E23" s="6" t="s">
+      <c r="F23" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="F23" s="6">
+      <c r="G23" s="6">
         <v>10000</v>
       </c>
-      <c r="G23" s="6" t="s">
+      <c r="H23" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="H23" s="6" t="s">
+      <c r="I23" s="6" t="s">
         <v>80</v>
       </c>
     </row>
@@ -1302,4 +1428,139 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{478B71DD-E84C-462E-964C-DA5C95539497}">
+  <dimension ref="A1:J4"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="9" max="9" width="17.90625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="21.81640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" ht="15.5" x14ac:dyDescent="0.4">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="F1" s="2"/>
+      <c r="G1" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="15.5" x14ac:dyDescent="0.4">
+      <c r="A2" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F2" s="2"/>
+      <c r="G2" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="15.5" x14ac:dyDescent="0.4">
+      <c r="A3" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="15" x14ac:dyDescent="0.35">
+      <c r="A4" s="1"/>
+      <c r="B4" s="6">
+        <v>20001</v>
+      </c>
+      <c r="C4" s="6">
+        <v>2</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="E4" s="6">
+        <v>1001</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G4" s="6">
+        <v>5</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="I4" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="J4" s="7" t="s">
+        <v>96</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Design/Excel/ET/Datas/Game/Items.xlsx
+++ b/Design/Excel/ET/Datas/Game/Items.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\ugit\myGameDevelopmentKit\Design\Excel\ET\Datas\Game\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACA39AAC-D8CD-4F8C-BF7A-8F06E82246F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4A0E79E-374F-4428-9824-FDB08A071B76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2660" yWindow="2660" windowWidth="19200" windowHeight="9970" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -340,7 +340,8 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>map,int,long</t>
+    <t>map,int,int#sep=,;</t>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
 </file>

--- a/Design/Excel/ET/Datas/Game/Items.xlsx
+++ b/Design/Excel/ET/Datas/Game/Items.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\ugit\myGameDevelopmentKit\Design\Excel\ET\Datas\Game\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4A0E79E-374F-4428-9824-FDB08A071B76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23E01FE8-9B59-40E4-BF3C-F9A678614B07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2660" yWindow="2660" windowWidth="19200" windowHeight="9970" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4740" yWindow="2730" windowWidth="19200" windowHeight="9970" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Herb" sheetId="2" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="98">
   <si>
     <t>##var</t>
   </si>
@@ -51,10 +51,6 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>Name</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>string</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -332,15 +328,15 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>10061,10;10081,10</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>##type</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>map,int,int#sep=,;</t>
+    <t>(map#sep=,;),int,long</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>10061,10</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -808,6 +804,7 @@
     <col min="6" max="6" width="11.08984375" customWidth="1"/>
     <col min="8" max="8" width="9.90625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="17.81640625" customWidth="1"/>
+    <col min="10" max="10" width="19.7265625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.4">
@@ -818,26 +815,24 @@
         <v>7</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>8</v>
-      </c>
+        <v>91</v>
+      </c>
+      <c r="D1" s="2"/>
       <c r="E1" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F1" s="2"/>
       <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.4">
@@ -850,9 +845,7 @@
       <c r="C2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>2</v>
-      </c>
+      <c r="D2" s="2"/>
       <c r="E2" s="2" t="s">
         <v>5</v>
       </c>
@@ -861,13 +854,13 @@
         <v>5</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>5</v>
+        <v>96</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.4">
@@ -876,28 +869,28 @@
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>4</v>
       </c>
       <c r="E3" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="G3" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="F3" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="G3" s="4" t="s">
+      <c r="H3" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="H3" s="4" t="s">
+      <c r="I3" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="I3" s="2" t="s">
-        <v>84</v>
-      </c>
       <c r="J3" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -909,25 +902,22 @@
         <v>1</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E4" s="6">
         <v>1001</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G4" s="6">
         <v>5</v>
       </c>
       <c r="H4" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="I4" s="6" t="s">
         <v>12</v>
-      </c>
-      <c r="I4" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="J4">
-        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -938,22 +928,22 @@
         <v>1</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E5" s="6">
         <v>1001</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G5" s="6">
         <v>8</v>
       </c>
       <c r="H5" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="I5" s="6" t="s">
         <v>15</v>
-      </c>
-      <c r="I5" s="6" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
@@ -964,22 +954,22 @@
         <v>1</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E6" s="6">
         <v>1002</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G6" s="6">
         <v>12</v>
       </c>
       <c r="H6" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="I6" s="6" t="s">
         <v>19</v>
-      </c>
-      <c r="I6" s="6" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
@@ -990,22 +980,22 @@
         <v>1</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E7" s="6">
         <v>1002</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G7" s="6">
         <v>15</v>
       </c>
       <c r="H7" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="I7" s="6" t="s">
         <v>22</v>
-      </c>
-      <c r="I7" s="6" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
@@ -1016,22 +1006,22 @@
         <v>1</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E8" s="6">
         <v>1003</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G8" s="6">
         <v>25</v>
       </c>
       <c r="H8" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="I8" s="6" t="s">
         <v>26</v>
-      </c>
-      <c r="I8" s="6" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
@@ -1042,22 +1032,22 @@
         <v>1</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E9" s="6">
         <v>1003</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G9" s="6">
         <v>25</v>
       </c>
       <c r="H9" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="I9" s="6" t="s">
         <v>29</v>
-      </c>
-      <c r="I9" s="6" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
@@ -1068,22 +1058,22 @@
         <v>1</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E10" s="6">
         <v>1003</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G10" s="6">
         <v>30</v>
       </c>
       <c r="H10" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="I10" s="6" t="s">
         <v>32</v>
-      </c>
-      <c r="I10" s="6" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
@@ -1094,22 +1084,22 @@
         <v>1</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E11" s="6">
         <v>2001</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G11" s="6">
         <v>50</v>
       </c>
       <c r="H11" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="I11" s="6" t="s">
         <v>36</v>
-      </c>
-      <c r="I11" s="6" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
@@ -1120,22 +1110,22 @@
         <v>1</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E12" s="6">
         <v>2001</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G12" s="6">
         <v>60</v>
       </c>
       <c r="H12" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="I12" s="6" t="s">
         <v>39</v>
-      </c>
-      <c r="I12" s="6" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
@@ -1146,22 +1136,22 @@
         <v>1</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E13" s="6">
         <v>2002</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G13" s="6">
         <v>80</v>
       </c>
       <c r="H13" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="I13" s="6" t="s">
         <v>43</v>
-      </c>
-      <c r="I13" s="6" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
@@ -1172,22 +1162,22 @@
         <v>1</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E14" s="6">
         <v>2002</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G14" s="6">
         <v>100</v>
       </c>
       <c r="H14" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="I14" s="6" t="s">
         <v>46</v>
-      </c>
-      <c r="I14" s="6" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
@@ -1198,22 +1188,22 @@
         <v>1</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E15" s="6">
         <v>2002</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G15" s="6">
         <v>100</v>
       </c>
       <c r="H15" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="I15" s="6" t="s">
         <v>49</v>
-      </c>
-      <c r="I15" s="6" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
@@ -1224,22 +1214,22 @@
         <v>1</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E16" s="6">
         <v>2003</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G16" s="6">
         <v>150</v>
       </c>
       <c r="H16" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="I16" s="6" t="s">
         <v>53</v>
-      </c>
-      <c r="I16" s="6" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.25">
@@ -1250,22 +1240,22 @@
         <v>1</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E17" s="6">
         <v>2003</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G17" s="6">
         <v>200</v>
       </c>
       <c r="H17" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="I17" s="6" t="s">
         <v>56</v>
-      </c>
-      <c r="I17" s="6" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="18" spans="2:9" x14ac:dyDescent="0.25">
@@ -1276,22 +1266,22 @@
         <v>1</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E18" s="6">
         <v>3001</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G18" s="6">
         <v>500</v>
       </c>
       <c r="H18" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="I18" s="6" t="s">
         <v>60</v>
-      </c>
-      <c r="I18" s="6" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="19" spans="2:9" x14ac:dyDescent="0.25">
@@ -1302,22 +1292,22 @@
         <v>1</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E19" s="6">
         <v>3002</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G19" s="6">
         <v>800</v>
       </c>
       <c r="H19" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="I19" s="6" t="s">
         <v>64</v>
-      </c>
-      <c r="I19" s="6" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.25">
@@ -1328,22 +1318,22 @@
         <v>1</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E20" s="6">
         <v>3002</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G20" s="6">
         <v>900</v>
       </c>
       <c r="H20" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="I20" s="6" t="s">
         <v>67</v>
-      </c>
-      <c r="I20" s="6" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="21" spans="2:9" x14ac:dyDescent="0.25">
@@ -1354,22 +1344,22 @@
         <v>1</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E21" s="6">
         <v>3003</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G21" s="6">
         <v>1500</v>
       </c>
       <c r="H21" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="I21" s="6" t="s">
         <v>71</v>
-      </c>
-      <c r="I21" s="6" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.25">
@@ -1380,22 +1370,22 @@
         <v>1</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E22" s="6">
         <v>4001</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G22" s="6">
         <v>3000</v>
       </c>
       <c r="H22" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="I22" s="6" t="s">
         <v>75</v>
-      </c>
-      <c r="I22" s="6" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="23" spans="2:9" x14ac:dyDescent="0.25">
@@ -1406,22 +1396,22 @@
         <v>1</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E23" s="6">
         <v>5001</v>
       </c>
       <c r="F23" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G23" s="6">
         <v>10000</v>
       </c>
       <c r="H23" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="I23" s="6" t="s">
         <v>79</v>
-      </c>
-      <c r="I23" s="6" t="s">
-        <v>80</v>
       </c>
     </row>
   </sheetData>
@@ -1448,31 +1438,29 @@
         <v>7</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>8</v>
-      </c>
+        <v>91</v>
+      </c>
+      <c r="D1" s="2"/>
       <c r="E1" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F1" s="2"/>
       <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="15.5" x14ac:dyDescent="0.4">
       <c r="A2" s="5" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>5</v>
@@ -1480,9 +1468,7 @@
       <c r="C2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>2</v>
-      </c>
+      <c r="D2" s="2"/>
       <c r="E2" s="2" t="s">
         <v>5</v>
       </c>
@@ -1491,13 +1477,13 @@
         <v>5</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="15.5" x14ac:dyDescent="0.4">
@@ -1506,28 +1492,28 @@
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>4</v>
       </c>
       <c r="E3" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="G3" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="F3" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>82</v>
-      </c>
       <c r="H3" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="15" x14ac:dyDescent="0.35">
@@ -1539,25 +1525,25 @@
         <v>2</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E4" s="6">
         <v>1001</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G4" s="6">
         <v>5</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="J4" s="7" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
   </sheetData>

--- a/Design/Excel/ET/Datas/Game/Items.xlsx
+++ b/Design/Excel/ET/Datas/Game/Items.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\ugit\myGameDevelopmentKit\Design\Excel\ET\Datas\Game\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23E01FE8-9B59-40E4-BF3C-F9A678614B07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6955AB5-2FF5-48D6-862D-26F134F5261B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4740" yWindow="2730" windowWidth="19200" windowHeight="9970" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Herb" sheetId="2" r:id="rId1"/>
@@ -336,7 +336,7 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>10061,10</t>
+    <t>10062,10</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>

--- a/Design/Excel/ET/Datas/Game/Items.xlsx
+++ b/Design/Excel/ET/Datas/Game/Items.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\ugit\myGameDevelopmentKit\Design\Excel\ET\Datas\Game\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6955AB5-2FF5-48D6-862D-26F134F5261B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{455CB620-7BF3-4AD9-BF22-81ACF8DED069}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Design/Excel/ET/Datas/Game/Items.xlsx
+++ b/Design/Excel/ET/Datas/Game/Items.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\ugit\myGameDevelopmentKit\Design\Excel\ET\Datas\Game\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{455CB620-7BF3-4AD9-BF22-81ACF8DED069}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{252D2721-2CD1-44DF-A245-8508BEDA343C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4070" yWindow="1760" windowWidth="19200" windowHeight="9970" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Herb" sheetId="2" r:id="rId1"/>

--- a/Design/Excel/ET/Datas/Game/Items.xlsx
+++ b/Design/Excel/ET/Datas/Game/Items.xlsx
@@ -8,20 +8,21 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\ugit\myGameDevelopmentKit\Design\Excel\ET\Datas\Game\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{252D2721-2CD1-44DF-A245-8508BEDA343C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7904BBD-4344-4559-AD2E-DCB7A1A4CE9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4070" yWindow="1760" windowWidth="19200" windowHeight="9970" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2210" yWindow="2070" windowWidth="19200" windowHeight="9970" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Herb" sheetId="2" r:id="rId1"/>
     <sheet name="Weapon" sheetId="3" r:id="rId2"/>
+    <sheet name="Other" sheetId="4" r:id="rId3"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="101">
   <si>
     <t>##var</t>
   </si>
@@ -337,6 +338,18 @@
   </si>
   <si>
     <t>10062,10</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>储物袋</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>家</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>40001,40</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -347,7 +360,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="0.00_);[Red]\(0.00\)"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -414,6 +427,12 @@
       <color rgb="FF9C0006"/>
       <name val="宋体"/>
       <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -1550,4 +1569,134 @@
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E609045-53A1-4CBE-A514-A7EAB2664AE2}">
+  <dimension ref="A1:J4"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="8" max="8" width="9.90625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.90625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="21.81640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" ht="15.5" x14ac:dyDescent="0.4">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="F1" s="2"/>
+      <c r="G1" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="15.5" x14ac:dyDescent="0.4">
+      <c r="A2" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F2" s="2"/>
+      <c r="G2" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="15.5" x14ac:dyDescent="0.4">
+      <c r="A3" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="15" x14ac:dyDescent="0.35">
+      <c r="A4" s="1"/>
+      <c r="B4" s="6">
+        <v>40001</v>
+      </c>
+      <c r="C4" s="6">
+        <v>4</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="E4" s="6">
+        <v>1001</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4" s="6">
+        <v>5</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="I4" s="6"/>
+      <c r="J4" s="7" t="s">
+        <v>100</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="9" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Design/Excel/ET/Datas/Game/Items.xlsx
+++ b/Design/Excel/ET/Datas/Game/Items.xlsx
@@ -1,28 +1,42 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\ugit\myGameDevelopmentKit\Design\Excel\ET\Datas\Game\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7904BBD-4344-4559-AD2E-DCB7A1A4CE9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB3C25E5-7318-41E2-A38E-3C5E706E46DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2210" yWindow="2070" windowWidth="19200" windowHeight="9970" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5550" yWindow="2240" windowWidth="19200" windowHeight="9970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Herb" sheetId="2" r:id="rId1"/>
     <sheet name="Weapon" sheetId="3" r:id="rId2"/>
-    <sheet name="Other" sheetId="4" r:id="rId3"/>
+    <sheet name="Medicine" sheetId="5" r:id="rId3"/>
+    <sheet name="Other" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="110">
   <si>
     <t>##var</t>
   </si>
@@ -334,10 +348,6 @@
   </si>
   <si>
     <t>(map#sep=,;),int,long</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>10062,10</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
@@ -351,6 +361,45 @@
   <si>
     <t>40001,40</t>
     <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Name</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>培元丹</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>凝血丹</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>增加血量</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>增加气量</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>10062,100</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>10062,100</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>10062,10</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>string</t>
+  </si>
+  <si>
+    <t>string</t>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -495,7 +544,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -506,6 +555,7 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="差" xfId="3" builtinId="27"/>
@@ -813,20 +863,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:J23"/>
+  <dimension ref="A1:K23"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="6.26953125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="8.90625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.90625" customWidth="1"/>
-    <col min="5" max="5" width="7.81640625" customWidth="1"/>
-    <col min="6" max="6" width="11.08984375" customWidth="1"/>
-    <col min="8" max="8" width="9.90625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="17.81640625" customWidth="1"/>
-    <col min="10" max="10" width="19.7265625" customWidth="1"/>
+    <col min="4" max="4" width="13.08984375" customWidth="1"/>
+    <col min="5" max="5" width="9.90625" customWidth="1"/>
+    <col min="6" max="6" width="7.81640625" customWidth="1"/>
+    <col min="7" max="7" width="11.08984375" customWidth="1"/>
+    <col min="9" max="9" width="9.90625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.81640625" customWidth="1"/>
+    <col min="11" max="11" width="19.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:11" ht="15.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -836,25 +887,28 @@
       <c r="C1" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2" t="s">
+      <c r="D1" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="F1" s="2"/>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="2"/>
+      <c r="H1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="I1" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="K1" s="2" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:11" ht="15.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="5" t="s">
         <v>1</v>
       </c>
@@ -864,25 +918,28 @@
       <c r="C2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2" t="s">
+      <c r="D2" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="2"/>
-      <c r="G2" s="4" t="s">
+      <c r="G2" s="2"/>
+      <c r="H2" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="I2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="J2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="K2" s="2" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:11" ht="15.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="3" t="s">
         <v>3</v>
       </c>
@@ -894,25 +951,28 @@
         <v>4</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>80</v>
+        <v>4</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="G3" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="H3" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="H3" s="4" t="s">
+      <c r="I3" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="J3" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="K3" s="2" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
       <c r="B4" s="6">
         <v>10001</v>
@@ -920,516 +980,596 @@
       <c r="C4" s="6">
         <v>1</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="6" t="str">
+        <f>_xlfn.CONCAT( "Item",B4)</f>
+        <v>Item10001</v>
+      </c>
+      <c r="E4" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="E4" s="6">
+      <c r="F4" s="6">
         <v>1001</v>
       </c>
-      <c r="F4" s="6" t="s">
+      <c r="G4" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="G4" s="6">
+      <c r="H4" s="6">
         <v>5</v>
       </c>
-      <c r="H4" s="6" t="s">
+      <c r="I4" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="I4" s="6" t="s">
+      <c r="J4" s="6" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="6">
         <v>10002</v>
       </c>
       <c r="C5" s="6">
         <v>1</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="6" t="str">
+        <f t="shared" ref="D5:D23" si="0">_xlfn.CONCAT( "Item",B5)</f>
+        <v>Item10002</v>
+      </c>
+      <c r="E5" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="6">
+      <c r="F5" s="6">
         <v>1001</v>
       </c>
-      <c r="F5" s="6" t="s">
+      <c r="G5" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="G5" s="6">
+      <c r="H5" s="6">
         <v>8</v>
       </c>
-      <c r="H5" s="6" t="s">
+      <c r="I5" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="I5" s="6" t="s">
+      <c r="J5" s="6" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B6" s="6">
         <v>10003</v>
       </c>
       <c r="C6" s="6">
         <v>1</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="D6" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>Item10003</v>
+      </c>
+      <c r="E6" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="E6" s="6">
+      <c r="F6" s="6">
         <v>1002</v>
       </c>
-      <c r="F6" s="6" t="s">
+      <c r="G6" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="G6" s="6">
+      <c r="H6" s="6">
         <v>12</v>
       </c>
-      <c r="H6" s="6" t="s">
+      <c r="I6" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="I6" s="6" t="s">
+      <c r="J6" s="6" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B7" s="6">
         <v>10004</v>
       </c>
       <c r="C7" s="6">
         <v>1</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="D7" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>Item10004</v>
+      </c>
+      <c r="E7" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="E7" s="6">
+      <c r="F7" s="6">
         <v>1002</v>
       </c>
-      <c r="F7" s="6" t="s">
+      <c r="G7" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="G7" s="6">
+      <c r="H7" s="6">
         <v>15</v>
       </c>
-      <c r="H7" s="6" t="s">
+      <c r="I7" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="I7" s="6" t="s">
+      <c r="J7" s="6" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B8" s="6">
         <v>10005</v>
       </c>
       <c r="C8" s="6">
         <v>1</v>
       </c>
-      <c r="D8" s="6" t="s">
+      <c r="D8" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>Item10005</v>
+      </c>
+      <c r="E8" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="E8" s="6">
+      <c r="F8" s="6">
         <v>1003</v>
       </c>
-      <c r="F8" s="6" t="s">
+      <c r="G8" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="G8" s="6">
+      <c r="H8" s="6">
         <v>25</v>
       </c>
-      <c r="H8" s="6" t="s">
+      <c r="I8" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="I8" s="6" t="s">
+      <c r="J8" s="6" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B9" s="6">
         <v>10006</v>
       </c>
       <c r="C9" s="6">
         <v>1</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="D9" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>Item10006</v>
+      </c>
+      <c r="E9" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="E9" s="6">
+      <c r="F9" s="6">
         <v>1003</v>
       </c>
-      <c r="F9" s="6" t="s">
+      <c r="G9" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="G9" s="6">
+      <c r="H9" s="6">
         <v>25</v>
       </c>
-      <c r="H9" s="6" t="s">
+      <c r="I9" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="I9" s="6" t="s">
+      <c r="J9" s="6" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B10" s="6">
         <v>10007</v>
       </c>
       <c r="C10" s="6">
         <v>1</v>
       </c>
-      <c r="D10" s="6" t="s">
+      <c r="D10" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>Item10007</v>
+      </c>
+      <c r="E10" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="E10" s="6">
+      <c r="F10" s="6">
         <v>1003</v>
       </c>
-      <c r="F10" s="6" t="s">
+      <c r="G10" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="G10" s="6">
+      <c r="H10" s="6">
         <v>30</v>
       </c>
-      <c r="H10" s="6" t="s">
+      <c r="I10" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="I10" s="6" t="s">
+      <c r="J10" s="6" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B11" s="6">
         <v>10008</v>
       </c>
       <c r="C11" s="6">
         <v>1</v>
       </c>
-      <c r="D11" s="6" t="s">
+      <c r="D11" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>Item10008</v>
+      </c>
+      <c r="E11" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="E11" s="6">
+      <c r="F11" s="6">
         <v>2001</v>
       </c>
-      <c r="F11" s="6" t="s">
+      <c r="G11" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="G11" s="6">
+      <c r="H11" s="6">
         <v>50</v>
       </c>
-      <c r="H11" s="6" t="s">
+      <c r="I11" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="I11" s="6" t="s">
+      <c r="J11" s="6" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B12" s="6">
         <v>10009</v>
       </c>
       <c r="C12" s="6">
         <v>1</v>
       </c>
-      <c r="D12" s="6" t="s">
+      <c r="D12" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>Item10009</v>
+      </c>
+      <c r="E12" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="E12" s="6">
+      <c r="F12" s="6">
         <v>2001</v>
       </c>
-      <c r="F12" s="6" t="s">
+      <c r="G12" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="G12" s="6">
+      <c r="H12" s="6">
         <v>60</v>
       </c>
-      <c r="H12" s="6" t="s">
+      <c r="I12" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="I12" s="6" t="s">
+      <c r="J12" s="6" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B13" s="6">
         <v>10010</v>
       </c>
       <c r="C13" s="6">
         <v>1</v>
       </c>
-      <c r="D13" s="6" t="s">
+      <c r="D13" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>Item10010</v>
+      </c>
+      <c r="E13" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="E13" s="6">
+      <c r="F13" s="6">
         <v>2002</v>
       </c>
-      <c r="F13" s="6" t="s">
+      <c r="G13" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="G13" s="6">
+      <c r="H13" s="6">
         <v>80</v>
       </c>
-      <c r="H13" s="6" t="s">
+      <c r="I13" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="I13" s="6" t="s">
+      <c r="J13" s="6" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B14" s="6">
         <v>10011</v>
       </c>
       <c r="C14" s="6">
         <v>1</v>
       </c>
-      <c r="D14" s="6" t="s">
+      <c r="D14" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>Item10011</v>
+      </c>
+      <c r="E14" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="E14" s="6">
+      <c r="F14" s="6">
         <v>2002</v>
       </c>
-      <c r="F14" s="6" t="s">
+      <c r="G14" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="G14" s="6">
+      <c r="H14" s="6">
         <v>100</v>
       </c>
-      <c r="H14" s="6" t="s">
+      <c r="I14" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="I14" s="6" t="s">
+      <c r="J14" s="6" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B15" s="6">
         <v>10012</v>
       </c>
       <c r="C15" s="6">
         <v>1</v>
       </c>
-      <c r="D15" s="6" t="s">
+      <c r="D15" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>Item10012</v>
+      </c>
+      <c r="E15" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="E15" s="6">
+      <c r="F15" s="6">
         <v>2002</v>
       </c>
-      <c r="F15" s="6" t="s">
+      <c r="G15" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="G15" s="6">
+      <c r="H15" s="6">
         <v>100</v>
       </c>
-      <c r="H15" s="6" t="s">
+      <c r="I15" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="I15" s="6" t="s">
+      <c r="J15" s="6" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B16" s="6">
         <v>10013</v>
       </c>
       <c r="C16" s="6">
         <v>1</v>
       </c>
-      <c r="D16" s="6" t="s">
+      <c r="D16" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>Item10013</v>
+      </c>
+      <c r="E16" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="E16" s="6">
+      <c r="F16" s="6">
         <v>2003</v>
       </c>
-      <c r="F16" s="6" t="s">
+      <c r="G16" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="G16" s="6">
+      <c r="H16" s="6">
         <v>150</v>
       </c>
-      <c r="H16" s="6" t="s">
+      <c r="I16" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="I16" s="6" t="s">
+      <c r="J16" s="6" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="17" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B17" s="6">
         <v>10014</v>
       </c>
       <c r="C17" s="6">
         <v>1</v>
       </c>
-      <c r="D17" s="6" t="s">
+      <c r="D17" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>Item10014</v>
+      </c>
+      <c r="E17" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="E17" s="6">
+      <c r="F17" s="6">
         <v>2003</v>
       </c>
-      <c r="F17" s="6" t="s">
+      <c r="G17" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="G17" s="6">
+      <c r="H17" s="6">
         <v>200</v>
       </c>
-      <c r="H17" s="6" t="s">
+      <c r="I17" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="I17" s="6" t="s">
+      <c r="J17" s="6" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="18" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B18" s="6">
         <v>10015</v>
       </c>
       <c r="C18" s="6">
         <v>1</v>
       </c>
-      <c r="D18" s="6" t="s">
+      <c r="D18" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>Item10015</v>
+      </c>
+      <c r="E18" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="E18" s="6">
+      <c r="F18" s="6">
         <v>3001</v>
       </c>
-      <c r="F18" s="6" t="s">
+      <c r="G18" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="G18" s="6">
+      <c r="H18" s="6">
         <v>500</v>
       </c>
-      <c r="H18" s="6" t="s">
+      <c r="I18" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="I18" s="6" t="s">
+      <c r="J18" s="6" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="19" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B19" s="6">
         <v>10016</v>
       </c>
       <c r="C19" s="6">
         <v>1</v>
       </c>
-      <c r="D19" s="6" t="s">
+      <c r="D19" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>Item10016</v>
+      </c>
+      <c r="E19" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="E19" s="6">
+      <c r="F19" s="6">
         <v>3002</v>
       </c>
-      <c r="F19" s="6" t="s">
+      <c r="G19" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="G19" s="6">
+      <c r="H19" s="6">
         <v>800</v>
       </c>
-      <c r="H19" s="6" t="s">
+      <c r="I19" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="I19" s="6" t="s">
+      <c r="J19" s="6" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="20" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B20" s="6">
         <v>10017</v>
       </c>
       <c r="C20" s="6">
         <v>1</v>
       </c>
-      <c r="D20" s="6" t="s">
+      <c r="D20" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>Item10017</v>
+      </c>
+      <c r="E20" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="E20" s="6">
+      <c r="F20" s="6">
         <v>3002</v>
       </c>
-      <c r="F20" s="6" t="s">
+      <c r="G20" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="G20" s="6">
+      <c r="H20" s="6">
         <v>900</v>
       </c>
-      <c r="H20" s="6" t="s">
+      <c r="I20" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="I20" s="6" t="s">
+      <c r="J20" s="6" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="21" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B21" s="6">
         <v>10018</v>
       </c>
       <c r="C21" s="6">
         <v>1</v>
       </c>
-      <c r="D21" s="6" t="s">
+      <c r="D21" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>Item10018</v>
+      </c>
+      <c r="E21" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="E21" s="6">
+      <c r="F21" s="6">
         <v>3003</v>
       </c>
-      <c r="F21" s="6" t="s">
+      <c r="G21" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="G21" s="6">
+      <c r="H21" s="6">
         <v>1500</v>
       </c>
-      <c r="H21" s="6" t="s">
+      <c r="I21" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="I21" s="6" t="s">
+      <c r="J21" s="6" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="22" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B22" s="6">
         <v>10019</v>
       </c>
       <c r="C22" s="6">
         <v>1</v>
       </c>
-      <c r="D22" s="6" t="s">
+      <c r="D22" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>Item10019</v>
+      </c>
+      <c r="E22" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="E22" s="6">
+      <c r="F22" s="6">
         <v>4001</v>
       </c>
-      <c r="F22" s="6" t="s">
+      <c r="G22" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="G22" s="6">
+      <c r="H22" s="6">
         <v>3000</v>
       </c>
-      <c r="H22" s="6" t="s">
+      <c r="I22" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="I22" s="6" t="s">
+      <c r="J22" s="6" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="23" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B23" s="6">
         <v>10020</v>
       </c>
       <c r="C23" s="6">
         <v>1</v>
       </c>
-      <c r="D23" s="6" t="s">
+      <c r="D23" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>Item10020</v>
+      </c>
+      <c r="E23" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="E23" s="6">
+      <c r="F23" s="6">
         <v>5001</v>
       </c>
-      <c r="F23" s="6" t="s">
+      <c r="G23" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="G23" s="6">
+      <c r="H23" s="6">
         <v>10000</v>
       </c>
-      <c r="H23" s="6" t="s">
+      <c r="I23" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="I23" s="6" t="s">
+      <c r="J23" s="6" t="s">
         <v>79</v>
       </c>
     </row>
@@ -1442,14 +1582,15 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{478B71DD-E84C-462E-964C-DA5C95539497}">
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:K5"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="9" max="9" width="17.90625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="21.81640625" customWidth="1"/>
+    <col min="4" max="4" width="10.26953125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.90625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="21.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="15.5" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:11" ht="15.5" x14ac:dyDescent="0.4">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1459,25 +1600,28 @@
       <c r="C1" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2" t="s">
+      <c r="D1" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="F1" s="2"/>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="2"/>
+      <c r="H1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="I1" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="K1" s="2" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="15.5" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:11" ht="15.5" x14ac:dyDescent="0.4">
       <c r="A2" s="5" t="s">
         <v>95</v>
       </c>
@@ -1487,25 +1631,28 @@
       <c r="C2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2" t="s">
+      <c r="D2" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="2"/>
-      <c r="G2" s="4" t="s">
+      <c r="G2" s="2"/>
+      <c r="H2" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="I2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="J2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="K2" s="2" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="15.5" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:11" ht="15.5" x14ac:dyDescent="0.4">
       <c r="A3" s="3" t="s">
         <v>3</v>
       </c>
@@ -1517,25 +1664,28 @@
         <v>4</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>80</v>
+        <v>4</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="G3" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="H3" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="H3" s="4" t="s">
+      <c r="I3" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="J3" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="K3" s="2" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="15" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:11" ht="15" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
       <c r="B4" s="6">
         <v>20001</v>
@@ -1543,27 +1693,34 @@
       <c r="C4" s="6">
         <v>2</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="6" t="str">
+        <f>_xlfn.CONCAT( "Item",B4)</f>
+        <v>Item20001</v>
+      </c>
+      <c r="E4" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="E4" s="6">
+      <c r="F4" s="6">
         <v>1001</v>
       </c>
-      <c r="F4" s="6" t="s">
+      <c r="G4" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="G4" s="6">
+      <c r="H4" s="6">
         <v>5</v>
       </c>
-      <c r="H4" s="6" t="s">
+      <c r="I4" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="I4" s="6" t="s">
+      <c r="J4" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="J4" s="7" t="s">
-        <v>97</v>
-      </c>
+      <c r="K4" s="8" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K5" s="8"/>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
@@ -1572,16 +1729,16 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E609045-53A1-4CBE-A514-A7EAB2664AE2}">
-  <dimension ref="A1:J4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0EB4AAD7-9068-4031-85A0-E09E52882DE2}">
+  <dimension ref="A1:K5"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="8" max="8" width="9.90625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="17.90625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="21.81640625" customWidth="1"/>
+    <col min="4" max="4" width="13.36328125" customWidth="1"/>
+    <col min="10" max="10" width="20" customWidth="1"/>
+    <col min="11" max="11" width="19.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="15.5" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:11" ht="15.5" x14ac:dyDescent="0.4">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1591,27 +1748,30 @@
       <c r="C1" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2" t="s">
+      <c r="D1" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="F1" s="2"/>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="2"/>
+      <c r="H1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="I1" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="K1" s="2" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="15.5" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:11" ht="15.5" x14ac:dyDescent="0.4">
       <c r="A2" s="5" t="s">
-        <v>95</v>
+        <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>5</v>
@@ -1619,25 +1779,28 @@
       <c r="C2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2" t="s">
+      <c r="D2" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="2"/>
-      <c r="G2" s="4" t="s">
+      <c r="G2" s="2"/>
+      <c r="H2" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="I2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="J2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="K2" s="2" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="15.5" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:11" ht="15.5" x14ac:dyDescent="0.4">
       <c r="A3" s="3" t="s">
         <v>3</v>
       </c>
@@ -1649,25 +1812,206 @@
         <v>4</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>80</v>
+        <v>4</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="G3" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="H3" s="4" t="s">
         <v>81</v>
       </c>
+      <c r="I3" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B4" s="6">
+        <v>30001</v>
+      </c>
+      <c r="C4" s="6">
+        <v>3</v>
+      </c>
+      <c r="D4" s="6" t="str">
+        <f>_xlfn.CONCAT( "Item",B4)</f>
+        <v>Item30001</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="F4" s="6">
+        <v>1001</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="H4" s="6">
+        <v>5</v>
+      </c>
+      <c r="I4" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="J4" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="K4" s="8" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B5" s="6">
+        <v>30002</v>
+      </c>
+      <c r="C5" s="6">
+        <v>3</v>
+      </c>
+      <c r="D5" s="6" t="str">
+        <f>_xlfn.CONCAT( "Item",B5)</f>
+        <v>Item30002</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="F5" s="6">
+        <v>1001</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="H5" s="6">
+        <v>5</v>
+      </c>
+      <c r="I5" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="J5" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="K5" s="8" t="s">
+        <v>106</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="9" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E609045-53A1-4CBE-A514-A7EAB2664AE2}">
+  <dimension ref="A1:K4"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="4" max="4" width="15.453125" customWidth="1"/>
+    <col min="9" max="9" width="9.90625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.90625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="21.81640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="15.5" x14ac:dyDescent="0.4">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="G1" s="2"/>
+      <c r="H1" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" ht="15.5" x14ac:dyDescent="0.4">
+      <c r="A2" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G2" s="2"/>
+      <c r="H2" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="15.5" x14ac:dyDescent="0.4">
+      <c r="A3" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>80</v>
+      </c>
       <c r="H3" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="I3" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="J3" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="K3" s="2" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="15" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:11" ht="28" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
       <c r="B4" s="6">
         <v>40001</v>
@@ -1675,24 +2019,28 @@
       <c r="C4" s="6">
         <v>4</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="6" t="str">
+        <f>_xlfn.CONCAT( "Item",B4)</f>
+        <v>Item40001</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="F4" s="6">
+        <v>1001</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="H4" s="6">
+        <v>5</v>
+      </c>
+      <c r="I4" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="E4" s="6">
-        <v>1001</v>
-      </c>
-      <c r="F4" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="G4" s="6">
-        <v>5</v>
-      </c>
-      <c r="H4" s="6" t="s">
+      <c r="J4" s="6"/>
+      <c r="K4" s="7" t="s">
         <v>99</v>
-      </c>
-      <c r="I4" s="6"/>
-      <c r="J4" s="7" t="s">
-        <v>100</v>
       </c>
     </row>
   </sheetData>

--- a/Design/Excel/ET/Datas/Game/Items.xlsx
+++ b/Design/Excel/ET/Datas/Game/Items.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\ugit\myGameDevelopmentKit\Design\Excel\ET\Datas\Game\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB3C25E5-7318-41E2-A38E-3C5E706E46DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4D20F4B-7FB6-464B-B045-EEDC575ECD6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5550" yWindow="2240" windowWidth="19200" windowHeight="9970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Herb" sheetId="2" r:id="rId1"/>
     <sheet name="Weapon" sheetId="3" r:id="rId2"/>
     <sheet name="Medicine" sheetId="5" r:id="rId3"/>
     <sheet name="Other" sheetId="4" r:id="rId4"/>
+    <sheet name="Book" sheetId="6" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="112">
   <si>
     <t>##var</t>
   </si>
@@ -399,6 +400,14 @@
   </si>
   <si>
     <t>string</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>1008,1</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>1001,1</t>
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
 </sst>
@@ -2011,7 +2020,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="28" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:11" ht="15" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
       <c r="B4" s="6">
         <v>40001</v>
@@ -2047,4 +2056,179 @@
   <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{22679835-C1F5-4996-9E7A-E21F2FAF9B9F}">
+  <dimension ref="A1:K6"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="4" max="4" width="18.08984375" customWidth="1"/>
+    <col min="11" max="11" width="19.81640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="15.5" x14ac:dyDescent="0.4">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="G1" s="2"/>
+      <c r="H1" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" ht="15.5" x14ac:dyDescent="0.4">
+      <c r="A2" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G2" s="2"/>
+      <c r="H2" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="15.5" x14ac:dyDescent="0.4">
+      <c r="A3" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B4" s="6">
+        <v>50001</v>
+      </c>
+      <c r="C4" s="6">
+        <v>5</v>
+      </c>
+      <c r="D4" s="6" t="str">
+        <f>_xlfn.CONCAT( "Item",B4)</f>
+        <v>Item50001</v>
+      </c>
+      <c r="E4" s="6"/>
+      <c r="F4" s="6">
+        <v>1001</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="H4" s="6">
+        <v>5</v>
+      </c>
+      <c r="I4" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="J4" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="K4" s="8" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B5" s="6">
+        <v>50002</v>
+      </c>
+      <c r="C5" s="6">
+        <v>5</v>
+      </c>
+      <c r="D5" s="6" t="str">
+        <f>_xlfn.CONCAT( "Item",B5)</f>
+        <v>Item50002</v>
+      </c>
+      <c r="E5" s="6"/>
+      <c r="F5" s="6">
+        <v>1001</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="H5" s="6">
+        <v>5</v>
+      </c>
+      <c r="I5" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="J5" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="K5" s="8" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K6" s="8"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Design/Excel/ET/Datas/Game/Items.xlsx
+++ b/Design/Excel/ET/Datas/Game/Items.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\ugit\myGameDevelopmentKit\Design\Excel\ET\Datas\Game\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4D20F4B-7FB6-464B-B045-EEDC575ECD6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2D11B47-47F7-4B53-8087-C72245B304EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
